--- a/full/sliding_window_results_window_6.xlsx
+++ b/full/sliding_window_results_window_6.xlsx
@@ -463,13 +463,13 @@
         <v>29.55</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>30.36665211731184</v>
       </c>
       <c r="D2" t="n">
-        <v>-29.55</v>
+        <v>0.8166521173118433</v>
       </c>
       <c r="E2" t="n">
-        <v>873.2025</v>
+        <v>0.6669206807099166</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.75</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>30.37306242910338</v>
       </c>
       <c r="D3" t="n">
-        <v>-29.75</v>
+        <v>0.6230624291033848</v>
       </c>
       <c r="E3" t="n">
-        <v>885.0625</v>
+        <v>0.3882067905602105</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.84</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>29.99066224781861</v>
       </c>
       <c r="D4" t="n">
-        <v>-29.84</v>
+        <v>0.1506622478186053</v>
       </c>
       <c r="E4" t="n">
-        <v>890.4256</v>
+        <v>0.02269911291775483</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.81</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>29.91958244196424</v>
       </c>
       <c r="D5" t="n">
-        <v>-29.81</v>
+        <v>0.1095824419642391</v>
       </c>
       <c r="E5" t="n">
-        <v>888.6360999999999</v>
+        <v>0.01200831158684582</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.92</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>29.89798823353122</v>
       </c>
       <c r="D6" t="n">
-        <v>-29.92</v>
+        <v>-0.02201176646878622</v>
       </c>
       <c r="E6" t="n">
-        <v>895.2064000000001</v>
+        <v>0.0004845178630763814</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.98</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>30.09988692223648</v>
       </c>
       <c r="D7" t="n">
-        <v>-29.98</v>
+        <v>0.1198869222364785</v>
       </c>
       <c r="E7" t="n">
-        <v>898.8004000000001</v>
+        <v>0.01437287412333543</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.04</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>30.16321211180252</v>
       </c>
       <c r="D8" t="n">
-        <v>-30.04</v>
+        <v>0.1232121118025233</v>
       </c>
       <c r="E8" t="n">
-        <v>902.4015999999999</v>
+        <v>0.01518122449483751</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.21</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>30.29750673130906</v>
       </c>
       <c r="D9" t="n">
-        <v>-30.21</v>
+        <v>0.0875067313090625</v>
       </c>
       <c r="E9" t="n">
-        <v>912.6441000000001</v>
+        <v>0.00765742802439646</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.22</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>30.44672696430774</v>
       </c>
       <c r="D10" t="n">
-        <v>-30.22</v>
+        <v>0.226726964307737</v>
       </c>
       <c r="E10" t="n">
-        <v>913.2483999999999</v>
+        <v>0.05140511634420183</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.38</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>30.29502784300016</v>
       </c>
       <c r="D11" t="n">
-        <v>-30.38</v>
+        <v>-0.08497215699984295</v>
       </c>
       <c r="E11" t="n">
-        <v>922.9444</v>
+        <v>0.00722026746520596</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.44</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>30.3556783217689</v>
       </c>
       <c r="D12" t="n">
-        <v>-30.44</v>
+        <v>-0.08432167823110248</v>
       </c>
       <c r="E12" t="n">
-        <v>926.5936</v>
+        <v>0.007110145419709582</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.48</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>30.53438401314706</v>
       </c>
       <c r="D13" t="n">
-        <v>-30.48</v>
+        <v>0.05438401314706098</v>
       </c>
       <c r="E13" t="n">
-        <v>929.0304</v>
+        <v>0.002957620885979702</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.69</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>30.63601958917854</v>
       </c>
       <c r="D14" t="n">
-        <v>-30.69</v>
+        <v>-0.05398041082146321</v>
       </c>
       <c r="E14" t="n">
-        <v>941.8761000000001</v>
+        <v>0.002913884752453942</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.75</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>30.17980980881382</v>
       </c>
       <c r="D15" t="n">
-        <v>-30.75</v>
+        <v>-0.5701901911861782</v>
       </c>
       <c r="E15" t="n">
-        <v>945.5625</v>
+        <v>0.3251168541249305</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.94</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>30.30393750451478</v>
       </c>
       <c r="D16" t="n">
-        <v>-30.94</v>
+        <v>-0.6360624954852234</v>
       </c>
       <c r="E16" t="n">
-        <v>957.2836000000001</v>
+        <v>0.4045754981628898</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.95</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>30.58400968609432</v>
       </c>
       <c r="D17" t="n">
-        <v>-30.95</v>
+        <v>-0.3659903139056802</v>
       </c>
       <c r="E17" t="n">
-        <v>957.9024999999999</v>
+        <v>0.1339489098727783</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.02</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>30.87614945704727</v>
       </c>
       <c r="D18" t="n">
-        <v>-31.02</v>
+        <v>-0.1438505429527304</v>
       </c>
       <c r="E18" t="n">
-        <v>962.2404</v>
+        <v>0.02069297870779532</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.12</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>31.1134232730596</v>
       </c>
       <c r="D19" t="n">
-        <v>-31.12</v>
+        <v>-0.006576726940398459</v>
       </c>
       <c r="E19" t="n">
-        <v>968.4544000000001</v>
+        <v>4.325333724856287e-05</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.28</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>31.16860810802609</v>
       </c>
       <c r="D20" t="n">
-        <v>-31.28</v>
+        <v>-0.1113918919739092</v>
       </c>
       <c r="E20" t="n">
-        <v>978.4384000000001</v>
+        <v>0.01240815359752706</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.38</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>31.33760770974518</v>
       </c>
       <c r="D21" t="n">
-        <v>-31.38</v>
+        <v>-0.04239229025482061</v>
       </c>
       <c r="E21" t="n">
-        <v>984.7044</v>
+        <v>0.001797106273048958</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.58</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>31.63689533939427</v>
       </c>
       <c r="D22" t="n">
-        <v>-31.58</v>
+        <v>0.05689533939427349</v>
       </c>
       <c r="E22" t="n">
-        <v>997.2963999999999</v>
+        <v>0.003237079644789569</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.65</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>31.57125835059635</v>
       </c>
       <c r="D23" t="n">
-        <v>-31.65</v>
+        <v>-0.07874164940365347</v>
       </c>
       <c r="E23" t="n">
-        <v>1001.7225</v>
+        <v>0.006200247350807881</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.88</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>31.902911412466</v>
       </c>
       <c r="D24" t="n">
-        <v>-31.88</v>
+        <v>0.02291141246600503</v>
       </c>
       <c r="E24" t="n">
-        <v>1016.3344</v>
+        <v>0.0005249328211874108</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>32.28</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>32.27999587101024</v>
       </c>
       <c r="D25" t="n">
-        <v>-32.28</v>
+        <v>-4.128989758100943e-06</v>
       </c>
       <c r="E25" t="n">
-        <v>1041.9984</v>
+        <v>1.704855642250248e-11</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>32.45</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>32.31492129653395</v>
       </c>
       <c r="D26" t="n">
-        <v>-32.45</v>
+        <v>-0.135078703466057</v>
       </c>
       <c r="E26" t="n">
-        <v>1053.0025</v>
+        <v>0.01824625613007096</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>32.85</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>33.33681736660397</v>
       </c>
       <c r="D27" t="n">
-        <v>-32.85</v>
+        <v>0.4868173666039723</v>
       </c>
       <c r="E27" t="n">
-        <v>1079.1225</v>
+        <v>0.2369911484272264</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>32.9</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>33.02364523339497</v>
       </c>
       <c r="D28" t="n">
-        <v>-32.9</v>
+        <v>0.1236452333949742</v>
       </c>
       <c r="E28" t="n">
-        <v>1082.41</v>
+        <v>0.01528814374129765</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>33.1</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>33.37918762896857</v>
       </c>
       <c r="D29" t="n">
-        <v>-33.1</v>
+        <v>0.2791876289685646</v>
       </c>
       <c r="E29" t="n">
-        <v>1095.61</v>
+        <v>0.07794573216908891</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>33.4</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>33.43665432956772</v>
       </c>
       <c r="D30" t="n">
-        <v>-33.4</v>
+        <v>0.03665432956772463</v>
       </c>
       <c r="E30" t="n">
-        <v>1115.56</v>
+        <v>0.001343539876059372</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>33.7</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>33.98856141008333</v>
       </c>
       <c r="D31" t="n">
-        <v>-33.7</v>
+        <v>0.2885614100833251</v>
       </c>
       <c r="E31" t="n">
-        <v>1135.69</v>
+        <v>0.08326768738927694</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>34.1</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>34.70679810123244</v>
       </c>
       <c r="D32" t="n">
-        <v>-34.1</v>
+        <v>0.6067981012324353</v>
       </c>
       <c r="E32" t="n">
-        <v>1162.81</v>
+        <v>0.3682039356592888</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>34.4</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>34.64649225017088</v>
       </c>
       <c r="D33" t="n">
-        <v>-34.4</v>
+        <v>0.2464922501708813</v>
       </c>
       <c r="E33" t="n">
-        <v>1183.36</v>
+        <v>0.06075842939430432</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>34.9</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>35.03841452557509</v>
       </c>
       <c r="D34" t="n">
-        <v>-34.9</v>
+        <v>0.1384145255750937</v>
       </c>
       <c r="E34" t="n">
-        <v>1218.01</v>
+        <v>0.01915858089017827</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>35.3</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>34.9147971642647</v>
       </c>
       <c r="D35" t="n">
-        <v>-35.3</v>
+        <v>-0.3852028357352992</v>
       </c>
       <c r="E35" t="n">
-        <v>1246.09</v>
+        <v>0.1483812246585159</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>35.7</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>35.13928856504177</v>
       </c>
       <c r="D36" t="n">
-        <v>-35.7</v>
+        <v>-0.5607114349582289</v>
       </c>
       <c r="E36" t="n">
-        <v>1274.49</v>
+        <v>0.3143973132929162</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>36.3</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>35.700520038417</v>
       </c>
       <c r="D37" t="n">
-        <v>-36.3</v>
+        <v>-0.5994799615829933</v>
       </c>
       <c r="E37" t="n">
-        <v>1317.69</v>
+        <v>0.3593762243395471</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>36.8</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>36.07152366051772</v>
       </c>
       <c r="D38" t="n">
-        <v>-36.8</v>
+        <v>-0.7284763394822775</v>
       </c>
       <c r="E38" t="n">
-        <v>1354.24</v>
+        <v>0.5306777771854985</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>37.3</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>37.06429871258559</v>
       </c>
       <c r="D39" t="n">
-        <v>-37.3</v>
+        <v>-0.2357012874144075</v>
       </c>
       <c r="E39" t="n">
-        <v>1391.29</v>
+        <v>0.05555509688880915</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>37.9</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>37.59373788371554</v>
       </c>
       <c r="D40" t="n">
-        <v>-37.9</v>
+        <v>-0.3062621162844579</v>
       </c>
       <c r="E40" t="n">
-        <v>1436.41</v>
+        <v>0.0937964838710348</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>38.5</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>38.34942907022938</v>
       </c>
       <c r="D41" t="n">
-        <v>-38.5</v>
+        <v>-0.1505709297706233</v>
       </c>
       <c r="E41" t="n">
-        <v>1482.25</v>
+        <v>0.02267160489198996</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>38.9</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>39.32514080133006</v>
       </c>
       <c r="D42" t="n">
-        <v>-38.9</v>
+        <v>0.425140801330059</v>
       </c>
       <c r="E42" t="n">
-        <v>1513.21</v>
+        <v>0.1807447009555647</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>39.4</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>40.0991865390098</v>
       </c>
       <c r="D43" t="n">
-        <v>-39.4</v>
+        <v>0.6991865390098013</v>
       </c>
       <c r="E43" t="n">
-        <v>1552.36</v>
+        <v>0.4888618163325044</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>39.9</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>40.5984031086222</v>
       </c>
       <c r="D44" t="n">
-        <v>-39.9</v>
+        <v>0.6984031086222018</v>
       </c>
       <c r="E44" t="n">
-        <v>1592.01</v>
+        <v>0.487766902133155</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>40.1</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>40.20863638200954</v>
       </c>
       <c r="D45" t="n">
-        <v>-40.1</v>
+        <v>0.1086363820095357</v>
       </c>
       <c r="E45" t="n">
-        <v>1608.01</v>
+        <v>0.01180186349612178</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>40.6</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>41.23139036539403</v>
       </c>
       <c r="D46" t="n">
-        <v>-40.6</v>
+        <v>0.6313903653940329</v>
       </c>
       <c r="E46" t="n">
-        <v>1648.36</v>
+        <v>0.3986537935124104</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>40.9</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>41.46436510051771</v>
       </c>
       <c r="D47" t="n">
-        <v>-40.9</v>
+        <v>0.5643651005177119</v>
       </c>
       <c r="E47" t="n">
-        <v>1672.81</v>
+        <v>0.3185079666823671</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>41.2</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>41.32579206646838</v>
       </c>
       <c r="D48" t="n">
-        <v>-41.2</v>
+        <v>0.125792066468378</v>
       </c>
       <c r="E48" t="n">
-        <v>1697.44</v>
+        <v>0.01582364398638484</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>41.5</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>40.99730796859584</v>
       </c>
       <c r="D49" t="n">
-        <v>-41.5</v>
+        <v>-0.502692031404159</v>
       </c>
       <c r="E49" t="n">
-        <v>1722.25</v>
+        <v>0.2526992784372399</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>41.8</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>41.2627089484069</v>
       </c>
       <c r="D50" t="n">
-        <v>-41.8</v>
+        <v>-0.537291051593094</v>
       </c>
       <c r="E50" t="n">
-        <v>1747.24</v>
+        <v>0.2886816741220128</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>42.2</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>41.65376525386564</v>
       </c>
       <c r="D51" t="n">
-        <v>-42.2</v>
+        <v>-0.5462347461343668</v>
       </c>
       <c r="E51" t="n">
-        <v>1780.84</v>
+        <v>0.2983723978844762</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-1702.24</v>
+        <v>0.9627802583703939</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>58754.575</v>
+        <v>7.255656205405317</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>1175.0915</v>
+        <v>0.1451131241081063</v>
       </c>
     </row>
   </sheetData>

--- a/full/sliding_window_results_window_6.xlsx
+++ b/full/sliding_window_results_window_6.xlsx
@@ -463,13 +463,13 @@
         <v>29.55</v>
       </c>
       <c r="C2" t="n">
-        <v>30.36665211731184</v>
+        <v>29.48082815048555</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8166521173118433</v>
+        <v>-0.0691718495144471</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6669206807099166</v>
+        <v>0.004784744765249316</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.75</v>
       </c>
       <c r="C3" t="n">
-        <v>30.37306242910338</v>
+        <v>29.66487032601285</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6230624291033848</v>
+        <v>-0.08512967398715077</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3882067905602105</v>
+        <v>0.007247061393158574</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.84</v>
       </c>
       <c r="C4" t="n">
-        <v>29.99066224781861</v>
+        <v>29.85360412466119</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1506622478186053</v>
+        <v>0.01360412466118532</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02269911291775483</v>
+        <v>0.0001850722077970707</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.81</v>
       </c>
       <c r="C5" t="n">
-        <v>29.91958244196424</v>
+        <v>29.7660149211675</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1095824419642391</v>
+        <v>-0.04398507883249891</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01200831158684582</v>
+        <v>0.001934687159901144</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.92</v>
       </c>
       <c r="C6" t="n">
-        <v>29.89798823353122</v>
+        <v>29.69369728029488</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.02201176646878622</v>
+        <v>-0.2263027197051244</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0004845178630763814</v>
+        <v>0.0512129209459361</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.98</v>
       </c>
       <c r="C7" t="n">
-        <v>30.09988692223648</v>
+        <v>29.91768579950373</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1198869222364785</v>
+        <v>-0.06231420049627445</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01437287412333543</v>
+        <v>0.003883059583489891</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.04</v>
       </c>
       <c r="C8" t="n">
-        <v>30.16321211180252</v>
+        <v>30.07280678614714</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1232121118025233</v>
+        <v>0.03280678614714461</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01518122449483751</v>
+        <v>0.001076285217304479</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.21</v>
       </c>
       <c r="C9" t="n">
-        <v>30.29750673130906</v>
+        <v>29.92199322185659</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0875067313090625</v>
+        <v>-0.2880067781434121</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00765742802439646</v>
+        <v>0.08294790425654862</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.22</v>
       </c>
       <c r="C10" t="n">
-        <v>30.44672696430774</v>
+        <v>29.97747710519328</v>
       </c>
       <c r="D10" t="n">
-        <v>0.226726964307737</v>
+        <v>-0.2425228948067186</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05140511634420183</v>
+        <v>0.05881735450543071</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.38</v>
       </c>
       <c r="C11" t="n">
-        <v>30.29502784300016</v>
+        <v>30.05237491161141</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.08497215699984295</v>
+        <v>-0.3276250883885865</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00722026746520596</v>
+        <v>0.1073381985416291</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.44</v>
       </c>
       <c r="C12" t="n">
-        <v>30.3556783217689</v>
+        <v>30.13560655728134</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.08432167823110248</v>
+        <v>-0.3043934427186592</v>
       </c>
       <c r="E12" t="n">
-        <v>0.007110145419709582</v>
+        <v>0.09265536797011766</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.48</v>
       </c>
       <c r="C13" t="n">
-        <v>30.53438401314706</v>
+        <v>30.40062294959056</v>
       </c>
       <c r="D13" t="n">
-        <v>0.05438401314706098</v>
+        <v>-0.07937705040944465</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002957620885979702</v>
+        <v>0.006300716131703517</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.69</v>
       </c>
       <c r="C14" t="n">
-        <v>30.63601958917854</v>
+        <v>30.63081894078647</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.05398041082146321</v>
+        <v>-0.059181059213536</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002913884752453942</v>
+        <v>0.003502397769636055</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.75</v>
       </c>
       <c r="C15" t="n">
-        <v>30.17980980881382</v>
+        <v>30.29394203458525</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5701901911861782</v>
+        <v>-0.4560579654147467</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3251168541249305</v>
+        <v>0.2079888678182383</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.94</v>
       </c>
       <c r="C16" t="n">
-        <v>30.30393750451478</v>
+        <v>30.66068003269143</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6360624954852234</v>
+        <v>-0.2793199673085667</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4045754981628898</v>
+        <v>0.07801964413725876</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.95</v>
       </c>
       <c r="C17" t="n">
-        <v>30.58400968609432</v>
+        <v>30.7765875568393</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3659903139056802</v>
+        <v>-0.1734124431606965</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1339489098727783</v>
+        <v>0.03007187544296179</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.02</v>
       </c>
       <c r="C18" t="n">
-        <v>30.87614945704727</v>
+        <v>30.99976313091616</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1438505429527304</v>
+        <v>-0.02023686908384192</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02069297870779532</v>
+        <v>0.0004095308703165571</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.12</v>
       </c>
       <c r="C19" t="n">
-        <v>31.1134232730596</v>
+        <v>31.16297703901077</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.006576726940398459</v>
+        <v>0.04297703901076488</v>
       </c>
       <c r="E19" t="n">
-        <v>4.325333724856287e-05</v>
+        <v>0.001847025882132807</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.28</v>
       </c>
       <c r="C20" t="n">
-        <v>31.16860810802609</v>
+        <v>31.32696581306328</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1113918919739092</v>
+        <v>0.0469658130632773</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01240815359752706</v>
+        <v>0.002205787596694708</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.38</v>
       </c>
       <c r="C21" t="n">
-        <v>31.33760770974518</v>
+        <v>31.44562616272016</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.04239229025482061</v>
+        <v>0.06562616272016086</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001797106273048958</v>
+        <v>0.004306793233373032</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.58</v>
       </c>
       <c r="C22" t="n">
-        <v>31.63689533939427</v>
+        <v>31.63408177230201</v>
       </c>
       <c r="D22" t="n">
-        <v>0.05689533939427349</v>
+        <v>0.05408177230201616</v>
       </c>
       <c r="E22" t="n">
-        <v>0.003237079644789569</v>
+        <v>0.002924838095327122</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.65</v>
       </c>
       <c r="C23" t="n">
-        <v>31.57125835059635</v>
+        <v>31.50921408086542</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.07874164940365347</v>
+        <v>-0.1407859191345793</v>
       </c>
       <c r="E23" t="n">
-        <v>0.006200247350807881</v>
+        <v>0.0198206750265683</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.88</v>
       </c>
       <c r="C24" t="n">
-        <v>31.902911412466</v>
+        <v>31.72898167397422</v>
       </c>
       <c r="D24" t="n">
-        <v>0.02291141246600503</v>
+        <v>-0.151018326025774</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0005249328211874108</v>
+        <v>0.02280653479562698</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>32.28</v>
       </c>
       <c r="C25" t="n">
-        <v>32.27999587101024</v>
+        <v>32.03420422036218</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.128989758100943e-06</v>
+        <v>-0.2457957796378167</v>
       </c>
       <c r="E25" t="n">
-        <v>1.704855642250248e-11</v>
+        <v>0.06041556528776217</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>32.45</v>
       </c>
       <c r="C26" t="n">
-        <v>32.31492129653395</v>
+        <v>32.00960868332395</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.135078703466057</v>
+        <v>-0.4403913166760489</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01824625613007096</v>
+        <v>0.193944511803664</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>32.85</v>
       </c>
       <c r="C27" t="n">
-        <v>33.33681736660397</v>
+        <v>33.10844968961342</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4868173666039723</v>
+        <v>0.2584496896134141</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2369911484272264</v>
+        <v>0.06679624206127008</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>32.9</v>
       </c>
       <c r="C28" t="n">
-        <v>33.02364523339497</v>
+        <v>32.69078896571015</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1236452333949742</v>
+        <v>-0.2092110342898437</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01528814374129765</v>
+        <v>0.04376925686862614</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>33.1</v>
       </c>
       <c r="C29" t="n">
-        <v>33.37918762896857</v>
+        <v>33.05983506902918</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2791876289685646</v>
+        <v>-0.04016493097081764</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07794573216908891</v>
+        <v>0.001613221679890546</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>33.4</v>
       </c>
       <c r="C30" t="n">
-        <v>33.43665432956772</v>
+        <v>33.17177520116345</v>
       </c>
       <c r="D30" t="n">
-        <v>0.03665432956772463</v>
+        <v>-0.2282247988365498</v>
       </c>
       <c r="E30" t="n">
-        <v>0.001343539876059372</v>
+        <v>0.05208655880398361</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>33.7</v>
       </c>
       <c r="C31" t="n">
-        <v>33.98856141008333</v>
+        <v>33.60095247339004</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2885614100833251</v>
+        <v>-0.09904752660996508</v>
       </c>
       <c r="E31" t="n">
-        <v>0.08326768738927694</v>
+        <v>0.009810412527551739</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>34.1</v>
       </c>
       <c r="C32" t="n">
-        <v>34.70679810123244</v>
+        <v>34.17623168047486</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6067981012324353</v>
+        <v>0.07623168047485507</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3682039356592888</v>
+        <v>0.005811269108020399</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>34.4</v>
       </c>
       <c r="C33" t="n">
-        <v>34.64649225017088</v>
+        <v>34.24123762031522</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2464922501708813</v>
+        <v>-0.1587623796847808</v>
       </c>
       <c r="E33" t="n">
-        <v>0.06075842939430432</v>
+        <v>0.0252054932031745</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>34.9</v>
       </c>
       <c r="C34" t="n">
-        <v>35.03841452557509</v>
+        <v>35.04036960806501</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1384145255750937</v>
+        <v>0.140369608065015</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01915858089017827</v>
+        <v>0.01970362686832592</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>35.3</v>
       </c>
       <c r="C35" t="n">
-        <v>34.9147971642647</v>
+        <v>34.80530223179038</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3852028357352992</v>
+        <v>-0.494697768209619</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1483812246585159</v>
+        <v>0.2447258818715779</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>35.7</v>
       </c>
       <c r="C36" t="n">
-        <v>35.13928856504177</v>
+        <v>35.29591176047898</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.5607114349582289</v>
+        <v>-0.4040882395210232</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3143973132929162</v>
+        <v>0.1632873053191999</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>36.3</v>
       </c>
       <c r="C37" t="n">
-        <v>35.700520038417</v>
+        <v>36.19296119968128</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.5994799615829933</v>
+        <v>-0.107038800318719</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3593762243395471</v>
+        <v>0.01145730477367061</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>36.8</v>
       </c>
       <c r="C38" t="n">
-        <v>36.07152366051772</v>
+        <v>36.56515541881418</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.7284763394822775</v>
+        <v>-0.2348445811858184</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5306777771854985</v>
+        <v>0.05515197731234246</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>37.3</v>
       </c>
       <c r="C39" t="n">
-        <v>37.06429871258559</v>
+        <v>37.25818969742834</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2357012874144075</v>
+        <v>-0.04181030257165474</v>
       </c>
       <c r="E39" t="n">
-        <v>0.05555509688880915</v>
+        <v>0.001748101401133319</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>37.9</v>
       </c>
       <c r="C40" t="n">
-        <v>37.59373788371554</v>
+        <v>37.86310629949936</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3062621162844579</v>
+        <v>-0.03689370050063445</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0937964838710348</v>
+        <v>0.001361145136630515</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>38.5</v>
       </c>
       <c r="C41" t="n">
-        <v>38.34942907022938</v>
+        <v>38.24049265812746</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1505709297706233</v>
+        <v>-0.259507341872542</v>
       </c>
       <c r="E41" t="n">
-        <v>0.02267160489198996</v>
+        <v>0.06734406048575238</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>38.9</v>
       </c>
       <c r="C42" t="n">
-        <v>39.32514080133006</v>
+        <v>38.71289732693845</v>
       </c>
       <c r="D42" t="n">
-        <v>0.425140801330059</v>
+        <v>-0.1871026730615526</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1807447009555647</v>
+        <v>0.03500741026677824</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>39.4</v>
       </c>
       <c r="C43" t="n">
-        <v>40.0991865390098</v>
+        <v>39.23549087192933</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6991865390098013</v>
+        <v>-0.1645091280706694</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4888618163325044</v>
+        <v>0.02706325321857191</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>39.9</v>
       </c>
       <c r="C44" t="n">
-        <v>40.5984031086222</v>
+        <v>39.59550994998659</v>
       </c>
       <c r="D44" t="n">
-        <v>0.6984031086222018</v>
+        <v>-0.3044900500134133</v>
       </c>
       <c r="E44" t="n">
-        <v>0.487766902133155</v>
+        <v>0.09271419055717095</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>40.1</v>
       </c>
       <c r="C45" t="n">
-        <v>40.20863638200954</v>
+        <v>40.33895213459193</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1086363820095357</v>
+        <v>0.2389521345919334</v>
       </c>
       <c r="E45" t="n">
-        <v>0.01180186349612178</v>
+        <v>0.05709812262604147</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>40.6</v>
       </c>
       <c r="C46" t="n">
-        <v>41.23139036539403</v>
+        <v>40.43080665770351</v>
       </c>
       <c r="D46" t="n">
-        <v>0.6313903653940329</v>
+        <v>-0.169193342296488</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3986537935124104</v>
+        <v>0.02862638707745654</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>40.9</v>
       </c>
       <c r="C47" t="n">
-        <v>41.46436510051771</v>
+        <v>41.02648825181625</v>
       </c>
       <c r="D47" t="n">
-        <v>0.5643651005177119</v>
+        <v>0.126488251816248</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3185079666823671</v>
+        <v>0.01599927784753057</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>41.2</v>
       </c>
       <c r="C48" t="n">
-        <v>41.32579206646838</v>
+        <v>41.44402213897362</v>
       </c>
       <c r="D48" t="n">
-        <v>0.125792066468378</v>
+        <v>0.2440221389736124</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01582364398638484</v>
+        <v>0.05954680430925698</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>41.5</v>
       </c>
       <c r="C49" t="n">
-        <v>40.99730796859584</v>
+        <v>41.14078202414342</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.502692031404159</v>
+        <v>-0.3592179758565806</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2526992784372399</v>
+        <v>0.1290375541784989</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>41.8</v>
       </c>
       <c r="C50" t="n">
-        <v>41.2627089484069</v>
+        <v>41.40787807627166</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.537291051593094</v>
+        <v>-0.3921219237283395</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2886816741220128</v>
+        <v>0.1537596030684137</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>42.2</v>
       </c>
       <c r="C51" t="n">
-        <v>41.65376525386564</v>
+        <v>41.71413703594322</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5462347461343668</v>
+        <v>-0.4858629640567784</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2983723978844762</v>
+        <v>0.2360628198420384</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.9627802583703939</v>
+        <v>-6.731242682874086</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>7.255656205405317</v>
+        <v>2.651434700850735</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.1451131241081063</v>
+        <v>0.0530286940170147</v>
       </c>
     </row>
   </sheetData>
